--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0068.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0068.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Long Journey</t>
+          <t>Hành Trình Xa</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Consensus</t>
+          <t>Thỏa thuận</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>test weapon</t>
+          <t>Thử nghiệm vũ khí</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Plasma Recoiler</t>
+          <t>Bộ Phản Lực Plasma</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Edge Direction</t>
+          <t>Hướng Đột Phá</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Intergalactic Gaze</t>
+          <t>Ánh Nhìn Liên Ngân Hà</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Meow!</t>
+          <t>Meo!</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Beyond the Cycle</t>
+          <t>Vượt Qua Vòng Luân Hồi</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Laughter Prevails</t>
+          <t>Tiếng cười át hết</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Crusade</t>
+          <t>Thánh Chiến</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Harmonious Vibrancy</t>
+          <t>Âm Thanh Hài Hòa</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Unified</t>
+          <t>Đồng nhất</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>test weapon</t>
+          <t>Thử nghiệm vũ khí</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>A Free Knight's Tarantella</t>
+          <t>Điệu Tarantella của Kỵ Sĩ Tự Do</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Preordained</t>
+          <t>Định Mệnh Đã An Bài</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Pale Gale</t>
+          <t>Cơn Gió Xanh Nhạt</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Intergalactic Gaze</t>
+          <t>Ánh Nhìn Liên Ngân Hà</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Rhetoric</t>
+          <t>Hùng Biện</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Alarcrity</t>
+          <t>Nhanh nhạy</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Lingering Summer Tune</t>
+          <t>Khúc Hạ Lưu Âm</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Omniscient</t>
+          <t>Thấu Thị</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Long Journey</t>
+          <t>Hành Trình Xa</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>Đoàn Kết</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>test weapon</t>
+          <t>Thử nghiệm vũ khí</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Ever-changing</t>
+          <t>Biến Đổi Không Ngừng</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Unstoppable</t>
+          <t>Không Thể Ngăn Cản</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Intergalactic Gaze</t>
+          <t>Ánh Nhìn Liên Ngân Hà</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Rhetoric</t>
+          <t>Hùng Biện</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Rejuvinate</t>
+          <t>Hồi Sinh</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Fool's Warble</t>
+          <t>Giọng Hót Ngu Ngốc</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Mastermind</t>
+          <t>Bậc thầy âm mưu</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Darkness Breaker</t>
+          <t>Kẻ Phá Bóng Tối</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Crusade</t>
+          <t>Thánh Chiến</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Collective Strength</t>
+          <t>Sức Mạnh Tập Thể.</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Celestial Blessing</t>
+          <t>Phước Lành Từ Trời</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Wallbreaker</t>
+          <t>Phá Tường</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Intergalactic Gaze</t>
+          <t>Ánh Nhìn Liên Ngân Hà</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Rhetoric</t>
+          <t>Hùng Biện</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Electric Amplification</t>
+          <t>Khuếch Đại Điện</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Pole of the Celestial Dome</t>
+          <t>Cực Trời</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Panorama</t>
+          <t>Bức tranh toàn cảnh</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Fish Catch</t>
+          <t>Bắt Cá</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Astral Evolvement</t>
+          <t>Tiến Hóa Tinh Tú</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Crusade</t>
+          <t>Thánh Chiến</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Homebuilder's Anthem</t>
+          <t>Khúc Ca Kiến Tạo Tổ Ấm</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Companionship</t>
+          <t>Tình đồng đội</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>test weapon</t>
+          <t>Thử nghiệm vũ khí</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>From the Deep</t>
+          <t>Từ Vực Sâu</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Luminous Protection</t>
+          <t>Lớp Che Chở Ánh Sáng</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Underworld Requiem</t>
+          <t>Khúc Requiem Địa Ngục</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Forgiving Resilience</t>
+          <t>Sức Mạnh Tha Thứ</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Intergalactic Gaze</t>
+          <t>Ánh Nhìn Liên Ngân Hà</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Rhetoric</t>
+          <t>Hùng Biện</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Persevere</t>
+          <t>Kiên trì lên</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Persevere</t>
+          <t>Kiên trì lên</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Persevere</t>
+          <t>Kiên trì lên</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Persevere</t>
+          <t>Kiên trì lên</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Persevere</t>
+          <t>Kiên trì lên</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Prologue</t>
+          <t>Khúc dạo đầu</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Prologue</t>
+          <t>Khúc dạo đầu</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Prologue</t>
+          <t>Khúc dạo đầu</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Prologue</t>
+          <t>Khúc dạo đầu</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Persevere</t>
+          <t>Kiên trì lên</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Prologue</t>
+          <t>Khúc dạo đầu</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Persevere</t>
+          <t>Kiên trì lên</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Persevere</t>
+          <t>Kiên trì lên</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Persevere</t>
+          <t>Kiên trì lên</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Persevere</t>
+          <t>Kiên trì lên</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Persevere</t>
+          <t>Kiên trì lên</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Stormy Resolution</t>
+          <t>Quyết Tâm Trong Bão Tố</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Stormy Resolution</t>
+          <t>Quyết Tâm Trong Bão Tố</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Stormy Resolution</t>
+          <t>Quyết Tâm Trong Bão Tố</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Stormy Resolution</t>
+          <t>Quyết Tâm Trong Bão Tố</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Persevere</t>
+          <t>Kiên trì lên</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Stormy Resolution</t>
+          <t>Quyết Tâm Trong Bão Tố</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Stormy Resolution</t>
+          <t>Quyết Tâm Trong Bão Tố</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Stormy Resolution</t>
+          <t>Quyết Tâm Trong Bão Tố</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Stormy Resolution</t>
+          <t>Quyết Tâm Trong Bão Tố</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Stormy Resolution</t>
+          <t>Quyết Tâm Trong Bão Tố</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Stormy Resolution</t>
+          <t>Quyết Tâm Trong Bão Tố</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Stormy Resolution</t>
+          <t>Quyết Tâm Trong Bão Tố</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Stormy Resolution</t>
+          <t>Quyết Tâm Trong Bão Tố</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Stormy Resolution</t>
+          <t>Quyết Tâm Trong Bão Tố</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Stormy Resolution</t>
+          <t>Quyết Tâm Trong Bão Tố</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Persevere</t>
+          <t>Kiên trì lên</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Stormy Resolution</t>
+          <t>Quyết Tâm Trong Bão Tố</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Stormy Resolution</t>
+          <t>Quyết Tâm Trong Bão Tố</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Stormy Resolution</t>
+          <t>Quyết Tâm Trong Bão Tố</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Stormy Resolution</t>
+          <t>Quyết Tâm Trong Bão Tố</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Stormy Resolution</t>
+          <t>Quyết Tâm Trong Bão Tố</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Stormy Resolution</t>
+          <t>Quyết Tâm Trong Bão Tố</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Vibrance</t>
+          <t>Sắc Màu Rực Rỡ</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Vibrance</t>
+          <t>Sắc Màu Rực Rỡ</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Vibrance</t>
+          <t>Sắc Màu Rực Rỡ</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Vibrance</t>
+          <t>Sắc Màu Rực Rỡ</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Persevere</t>
+          <t>Kiên trì lên</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Vibrance</t>
+          <t>Sắc Màu Rực Rỡ</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Cadence</t>
+          <t>Nhịp điệu</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Cadence</t>
+          <t>Nhịp điệu</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Cadence</t>
+          <t>Nhịp điệu</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Cadence</t>
+          <t>Nhịp điệu</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Cadence</t>
+          <t>Nhịp điệu</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Ceaseless Aria</t>
+          <t>Khúc Aria Vô Tận</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Ceaseless Aria</t>
+          <t>Khúc Aria Vô Tận</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Ceaseless Aria</t>
+          <t>Khúc Aria Vô Tận</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Ceaseless Aria</t>
+          <t>Khúc Aria Vô Tận</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Persevere</t>
+          <t>Kiên trì lên</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Ceaseless Aria</t>
+          <t>Khúc Aria Vô Tận</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Zeal</t>
+          <t>Nhiệt Huyết</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Zeal</t>
+          <t>Nhiệt Huyết</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Zeal</t>
+          <t>Nhiệt Huyết</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Zeal</t>
+          <t>Nhiệt Huyết</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Zeal</t>
+          <t>Nhiệt Huyết</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Triumph</t>
+          <t>Chiến Thắng</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Triumph</t>
+          <t>Chiến Thắng</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Triumph</t>
+          <t>Chiến Thắng</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Triumph</t>
+          <t>Chiến Thắng</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Persevere</t>
+          <t>Kiên trì lên</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Triumph</t>
+          <t>Chiến Thắng</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Valiance</t>
+          <t>Dũng Khí</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Valiance</t>
+          <t>Dũng Khí</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Valiance</t>
+          <t>Dũng Khí</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Valiance</t>
+          <t>Dũng Khí</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Persevere</t>
+          <t>Kiên trì lên</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Valiance</t>
+          <t>Dũng Khí</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Valiance</t>
+          <t>Dũng Khí</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Valiance</t>
+          <t>Dũng Khí</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Valiance</t>
+          <t>Dũng Khí</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Valiance</t>
+          <t>Dũng Khí</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Valiance</t>
+          <t>Dũng Khí</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Valiance</t>
+          <t>Dũng Khí</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Valiance</t>
+          <t>Dũng Khí</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Valiance</t>
+          <t>Dũng Khí</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Valiance</t>
+          <t>Dũng Khí</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Suturing Dayline</t>
+          <t>Ngày Kết Nối</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Sunward</t>
+          <t>Hướng về mặt trời</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Dissolution</t>
+          <t>Sự phân rã</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Persevere</t>
+          <t>Kiên trì lên</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Bộ đếm Chi: Kích hoạt khi bị tấn công trong Calming Air</t>
+          <t>Bộ Đếm Chi: Kích hoạt khi bị tấn công trong trạng thái Gió Lặng</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Tăng ATK</t>
+          <t>ATK +10%</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Starchaser</t>
+          <t>Kẻ Đuổi Sao</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Self Không More</t>
+          <t>Không Còn Là Chính Mình</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12685,7 +12685,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Silent Eulogy</t>
+          <t>Lời Ai Điếu Vô Thanh</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Everbright Polestar</t>
+          <t>Ngôi Sao Bắc Đẩu Vĩnh Hằng</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12965,7 +12965,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Solsworn Ciphers</t>
+          <t>Mật Ngữ Solsworn</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13105,7 +13105,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Frostburn</t>
+          <t>Bỏng Sương</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13245,7 +13245,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Sắp xếp theo Chất lượng</t>
+          <t>Sắp xếp theo Chất Lượng</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13315,7 +13315,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Mô-đun Rarity</t>
+          <t>Độ Hiếm Mô-đun</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13385,7 +13385,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Thưởng Chỉ Số</t>
+          <t>Tăng thuộc tính</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13455,7 +13455,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Mô-đun Rarity</t>
+          <t>Độ Hiếm Mô-đun</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -14367,7 +14367,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Hiệu ứng Độc nhất: Dodge Counter giảm Cooldown của Kỹ năng Hỗ trợ Namipon đi &lt;color=Highlight&gt;{0}&lt;/color&gt; giây. Hiệu ứng này có thể kích hoạt &lt;color=Highlight&gt;&lt;SapTag=2&gt;{2}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=time P=times SapTag=2} mỗi &lt;color=Highlight&gt;{1}&lt;/color&gt; giây.</t>
+          <t>Hiệu ứng Độc nhất: Dodge Counter giảm Thời gian hồi của Kỹ năng Hỗ trợ Namipon đi &lt;color=Highlight&gt;{0}&lt;/color&gt; giây. Hiệu ứng này có thể kích hoạt &lt;color=Highlight&gt;&lt;SapTag=2&gt;{2}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=time P=times SapTag=2} mỗi &lt;color=Highlight&gt;{1}&lt;/color&gt; giây.</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14789,7 +14789,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Hiệu ứng Độc nhất: Dodge Counter giảm Cooldown của Kỹ năng Hỗ trợ Namipon đi &lt;color=Highlight&gt;{0}&lt;/color&gt; giây. Hiệu ứng này có thể kích hoạt &lt;color=Highlight&gt;&lt;SapTag=2&gt;{2}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=time P=times SapTag=2} mỗi &lt;color=Highlight&gt;{1}&lt;/color&gt; giây.</t>
+          <t>Hiệu ứng Độc nhất: Dodge Counter giảm Thời gian hồi của Kỹ năng Hỗ trợ Namipon đi &lt;color=Highlight&gt;{0}&lt;/color&gt; giây. Hiệu ứng này có thể kích hoạt &lt;color=Highlight&gt;&lt;SapTag=2&gt;{2}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=time P=times SapTag=2} mỗi &lt;color=Highlight&gt;{1}&lt;/color&gt; giây.</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -16399,7 +16399,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Hiệu ứng Đặc biệt: Mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; lần Basic Attack gây DMG, Cooldown của Namipon Hỗ Trợ Skill sẽ giảm &lt;color=Highlight&gt;{1}&lt;/color&gt; giây (nhiều lần gây sát thương trong vòng &lt;color=Highlight&gt;{2}&lt;/color&gt; giây chỉ được tính là &lt;color=Highlight&gt;{3}&lt;/color&gt; lần gây sát thương).</t>
+          <t>Hiệu ứng Đặc biệt: Mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; lần Basic Attack gây DMG, Thời gian hồi của Namipon Hỗ Trợ Skill sẽ giảm &lt;color=Highlight&gt;{1}&lt;/color&gt; giây (nhiều lần gây sát thương trong vòng &lt;color=Highlight&gt;{2}&lt;/color&gt; giây chỉ được tính là &lt;color=Highlight&gt;{3}&lt;/color&gt; lần gây sát thương).</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -17449,7 +17449,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Hiệu ứng Đặc Biệt: Basic Attack hồi phục thêm &lt;color=Highlight&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=điểm P=điểm SapTag=0} Concerto Energy. Cooldown: &lt;color=Highlight&gt;{1}&lt;/color&gt; giây.</t>
+          <t>Hiệu ứng Đặc Biệt: Basic Attack hồi phục thêm &lt;color=Highlight&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=điểm P=điểm SapTag=0} Concerto Energy. Thời gian hồi: &lt;color=Highlight&gt;{1}&lt;/color&gt; giây.</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17659,7 +17659,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Hiệu ứng Đặc biệt: Basic Attack phục hồi thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; điểm Concerto Energy. Cooldown: &lt;color=Highlight&gt;{1}&lt;/color&gt; giây.</t>
+          <t>Hiệu ứng Đặc biệt: Basic Attack phục hồi thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; điểm Concerto Energy. Thời gian hồi: &lt;color=Highlight&gt;{1}&lt;/color&gt; giây.</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -18079,7 +18079,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Hiệu ứng Đặc biệt: Khi Độ Stability đạt trạng thái Nguy Kịch, Cooldown chiêu Resonance Skill sẽ giảm &lt;color=Highlight&gt;{0} giây&lt;/color&gt; mỗi khi sử dụng Skill Basic, kích hoạt tối đa &lt;color=Highlight&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lần P=lần SapTag=1} mỗi giây.</t>
+          <t>Hiệu ứng Đặc biệt: Khi Độ Stability đạt trạng thái Nguy Kịch, Thời gian hồi chiêu Resonance Skill sẽ giảm &lt;color=Highlight&gt;{0} giây&lt;/color&gt; mỗi khi sử dụng Skill Basic, kích hoạt tối đa &lt;color=Highlight&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lần P=lần SapTag=1} mỗi giây.</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18289,7 +18289,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Hiệu ứng Đặc biệt: Kích hoạt Outro Skill phục hồi &lt;color=Highlight&gt;{0}&lt;/color&gt; điểm Concerto Energy cho Resonator tiếp theo. Cooldown: &lt;color=Highlight&gt;{1}&lt;/color&gt; giây.</t>
+          <t>Hiệu ứng Đặc biệt: Kích hoạt Outro Skill phục hồi &lt;color=Highlight&gt;{0}&lt;/color&gt; điểm Concerto Energy cho Resonator tiếp theo. Thời gian hồi: &lt;color=Highlight&gt;{1}&lt;/color&gt; giây.</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18779,7 +18779,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Hiệu ứng Đặc biệt: Kích hoạt Resonance Liberation sẽ đặt lại Cooldown chiêu và hồi toàn bộ Năng lượng Resonance, kích hoạt &lt;color=Highlight&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lần P=lần SapTag=1} mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; giây.</t>
+          <t>Hiệu ứng Đặc biệt: Kích hoạt Resonance Liberation sẽ đặt lại Thời gian hồi chiêu và hồi toàn bộ Năng lượng Resonance, kích hoạt &lt;color=Highlight&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lần P=lần SapTag=1} mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; giây.</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -19759,7 +19759,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Hiệu ứng Đặc biệt: Dodge Counter giảm Cooldown của Kỹ năng Hỗ trợ Namipon.</t>
+          <t>Hiệu ứng Đặc biệt: Dodge Counter giảm Thời gian hồi của Kỹ năng Hỗ trợ Namipon.</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -20179,7 +20179,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Hiệu ứng Đặc biệt: Dodge Counter giảm Cooldown của Kỹ năng Hỗ trợ Namipon.</t>
+          <t>Hiệu ứng Đặc biệt: Dodge Counter giảm Thời gian hồi của Kỹ năng Hỗ trợ Namipon.</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -21369,7 +21369,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Hiệu ứng Đặc biệt: Mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; lần Basic Attack gây DMG sẽ giảm Cooldown Kỹ năng Hỗ trợ Namipon.</t>
+          <t>Hiệu ứng Đặc biệt: Mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; lần Basic Attack gây DMG sẽ giảm Thời gian hồi Kỹ năng Hỗ trợ Namipon.</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Hiệu ứng Đặc biệt: Mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; lần Basic Attack gây DMG sẽ giảm Cooldown Kỹ năng Hỗ trợ Namipon.</t>
+          <t>Hiệu ứng Đặc biệt: Mỗi &lt;color=Highlight&gt;{0}&lt;/color&gt; lần Basic Attack gây DMG sẽ giảm Thời gian hồi Kỹ năng Hỗ trợ Namipon.</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -23469,7 +23469,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Hiệu ứng Đặc biệt: Khi **Stability** đạt trạng thái **Critical State**, **Cooldown** của **Resonance Skill** giảm mỗi khi thực hiện **Basic Attack**.</t>
+          <t>Hiệu ứng Đặc biệt: Khi **Stability** đạt trạng thái **Critical State**, **Thời gian hồi** của **Resonance Skill** giảm mỗi khi thực hiện **Basic Attack**.</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -24169,7 +24169,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Hiệu ứng Đặc biệt: Kích hoạt **Resonance Liberation** sẽ đặt lại **Cooldown** và phục hồi toàn bộ **Resonance Energy**.</t>
+          <t>Hiệu ứng Đặc biệt: Kích hoạt **Resonance Liberation** sẽ đặt lại **Thời gian hồi** và phục hồi toàn bộ **Resonance Energy**.</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -26269,7 +26269,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Lift</t>
+          <t>Nâng lên</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26339,7 +26339,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Nose Down</t>
+          <t>Hạ Mũi Xuống</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26409,7 +26409,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Enhancement: Negative Status</t>
+          <t>Nâng Cấp: Negative Status</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26479,7 +26479,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Enhancement: Tune Break</t>
+          <t>Tăng Cường: Đột Phá Tần Số</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26549,7 +26549,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Enhancement: Shield</t>
+          <t>Nâng Cấp: Khiên</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26619,7 +26619,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Enhancement: Heavy Attack</t>
+          <t>Nâng Cấp: Heavy Attack</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26689,7 +26689,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Enhancement: Basic Attack</t>
+          <t>Nâng Cấp: Đòn Basic Attack</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26759,7 +26759,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Enhancement: Resonance Skill</t>
+          <t>Nâng Cấp: Resonance Skill</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26829,7 +26829,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Enhancement: Resonance Liberation</t>
+          <t>Nâng Cấp: Resonance Liberation</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26899,7 +26899,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Enhancement: Echo Skill</t>
+          <t>Nâng Cấp: Echo Skill</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26969,7 +26969,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>General Enhancement</t>
+          <t>Tăng Cường Tổng Hợp</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -29699,7 +29699,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Enhancement: Negative Status</t>
+          <t>Nâng Cấp: Negative Status</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29769,7 +29769,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Enhancement: Echo Skill</t>
+          <t>Nâng Cấp: Echo Skill</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29839,7 +29839,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Enhancement: Tune Break</t>
+          <t>Tăng Cường: Đột Phá Tần Số</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Instant Response</t>
+          <t>Phản ứng tức thì</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29979,7 +29979,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Stardust Resonance</t>
+          <t>Cộng Hưởng Stardust</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30049,7 +30049,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Heavenfall Edict: Unbound</t>
+          <t>Thiên Lệnh Cú Đổ: Giải Phóng</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30119,7 +30119,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Synchronization Rate</t>
+          <t>Tỷ Lệ Đồng Bộ</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30189,7 +30189,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Resonance Rate</t>
+          <t>Tỷ Lệ Cộng Hưởng</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30259,7 +30259,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Starlume Acceleration</t>
+          <t>Tăng Tốc Sao Sáng</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30329,7 +30329,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Seraphic Duet</t>
+          <t>Song Tấu Seraphic</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30399,7 +30399,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Sync Strike</t>
+          <t>Đòn Đồng Bộ</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30469,7 +30469,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Starflux</t>
+          <t>Dòng Sao</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30539,7 +30539,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Rupturous Trail</t>
+          <t>Dấu Vết Cuồng Nhiệt</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30609,7 +30609,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Fusion Trail</t>
+          <t>Vệt Hợp Thể</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30679,7 +30679,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Endnotes on the Endgame</t>
+          <t>Ghi chú cuối cùng về Trận Chiến Cuối</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30749,7 +30749,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Ichor Flow</t>
+          <t>Dòng Dưỡng Chất</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30819,7 +30819,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Dawnlit Keep</t>
+          <t>Thành Bình Minh Rạng Rỡ</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30889,7 +30889,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>General Enhancement</t>
+          <t>Tăng Cường Tổng Hợp</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30959,7 +30959,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Ichor Blade</t>
+          <t>Kiếm Dịch Huyết</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31029,7 +31029,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Ichor Deposit</t>
+          <t>Kho Dưỡng Chất</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31099,7 +31099,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Enhancement: Negative Status</t>
+          <t>Nâng Cấp: Negative Status</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31169,7 +31169,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Enhancement: Echo Skill</t>
+          <t>Nâng Cấp: Echo Skill</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31239,7 +31239,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Enhancement: Tune Break</t>
+          <t>Tăng Cường: Đột Phá Tần Số</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31309,7 +31309,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>General Enhancement</t>
+          <t>Tăng Cường Tổng Hợp</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31379,7 +31379,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Tune Break</t>
+          <t>Đột phá Điệu nhạc</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31449,7 +31449,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Chung</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31589,7 +31589,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Cycle Tasks</t>
+          <t>Nhiệm Vụ Chu Kỳ</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31729,7 +31729,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Rune</t>
+          <t>Bùa</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31799,7 +31799,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Full Stop</t>
+          <t>Dừng Hẳn</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31939,7 +31939,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Divergent</t>
+          <t>Giao Dị</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32009,7 +32009,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Convergent</t>
+          <t>Hội tụ</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32079,7 +32079,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Soliskin Vitality</t>
+          <t>Sinh Khí Soliskin</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32149,7 +32149,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Decipher</t>
+          <t>Giải mã</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32219,7 +32219,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Encapsulated</t>
+          <t>Bao bọc</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32289,7 +32289,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Enhancement: Negative Status</t>
+          <t>Nâng Cấp: Negative Status</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32359,7 +32359,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Enhancement: Echo Skill</t>
+          <t>Nâng Cấp: Echo Skill</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32429,7 +32429,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Enhancement: Tune Break</t>
+          <t>Tăng Cường: Đột Phá Tần Số</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32499,7 +32499,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>General Enhancement</t>
+          <t>Tăng Cường Tổng Hợp</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32569,7 +32569,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Dark Core</t>
+          <t>Lõi Hắc Ám</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32639,7 +32639,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Void Particle</t>
+          <t>Hạt Hư Không</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32709,7 +32709,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Entropy Shift: Breakdown Form</t>
+          <t>Dịch Chuyển Hỗn Độn: Hình Thái Phân Rã</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32779,7 +32779,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Entropy Shift: Stagecraft Form</t>
+          <t>Dịch Chuyển Hỗn Độn: Hình Thái Kỹ Xảo</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32849,7 +32849,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Conformal Charge</t>
+          <t>Điện Tích Đồng Dạng</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32919,7 +32919,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Dedication</t>
+          <t>Sự Cống Hiến</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32989,7 +32989,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Frostheart</t>
+          <t>Trái Tim Băng Giá</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33059,7 +33059,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Frostharden Iai</t>
+          <t>Iai Cứng Băng</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33129,7 +33129,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Whiteout Bitterfrost</t>
+          <t>Băng Giá Trắng Xóa</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33199,7 +33199,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Snowforged Blade</t>
+          <t>Thanh Kiếm Rèn Từ Tuyết</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33269,7 +33269,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Present Self</t>
+          <t>Bản Ngã Hiện Tại</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33339,7 +33339,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Foreclaimed Self</t>
+          <t>Bản Ngã Đã Định Trước</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33409,7 +33409,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Frostbind</t>
+          <t>Trói băng</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33479,7 +33479,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Entropy Shift</t>
+          <t>Dịch Chuyển Hỗn Độn</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33619,7 +33619,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Zone I</t>
+          <t>Khu I</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33689,7 +33689,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Zone II</t>
+          <t>Khu II</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33759,7 +33759,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Zone III</t>
+          <t>Khu III</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33829,7 +33829,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Zone IV</t>
+          <t>Khu IV</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33899,7 +33899,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Zone V</t>
+          <t>Khu V</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -35369,7 +35369,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Banner of Conquest: Medium 1</t>
+          <t>Ngọn Cờ Chinh Phục: Chiến Dịch Trung 1</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35439,7 +35439,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Banner of Conquest: Medium 10</t>
+          <t>Ngọn Cờ Chinh Phục: Chiến Dịch Trung 10</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35509,7 +35509,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Banner of Conquest: Major 11</t>
+          <t>Ngọn Cờ Chinh Phục: Cao 11</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
